--- a/Database.xlsx
+++ b/Database.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Charlie\Non Puriel\Adress-Shack\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6D364736-6C43-4BE9-8E8A-22222979A52C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6E61C24-B86A-4C35-883D-A7845DEEA5F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="80">
   <si>
     <t>Index</t>
   </si>
@@ -263,6 +263,24 @@
   </si>
   <si>
     <t>info</t>
+  </si>
+  <si>
+    <t>numeric</t>
+  </si>
+  <si>
+    <t>varchar</t>
+  </si>
+  <si>
+    <t>char(10)</t>
+  </si>
+  <si>
+    <t>bit</t>
+  </si>
+  <si>
+    <t>size</t>
+  </si>
+  <si>
+    <t>?</t>
   </si>
 </sst>
 </file>
@@ -991,7 +1009,49 @@
         <v>52</v>
       </c>
     </row>
-    <row r="23" spans="16:29" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="18" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>79</v>
+      </c>
+      <c r="B18" t="s">
+        <v>79</v>
+      </c>
+      <c r="C18" t="s">
+        <v>79</v>
+      </c>
+      <c r="D18">
+        <v>10</v>
+      </c>
+      <c r="E18">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="19" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>74</v>
+      </c>
+      <c r="B19" t="s">
+        <v>75</v>
+      </c>
+      <c r="C19" t="s">
+        <v>75</v>
+      </c>
+      <c r="D19" t="s">
+        <v>76</v>
+      </c>
+      <c r="E19" t="s">
+        <v>75</v>
+      </c>
+      <c r="F19" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="23" spans="1:29" x14ac:dyDescent="0.25">
       <c r="P23" s="1"/>
       <c r="W23" t="s">
         <v>53</v>
@@ -1015,7 +1075,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="16:29" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:29" x14ac:dyDescent="0.25">
       <c r="W24" t="s">
         <v>22</v>
       </c>

--- a/Database.xlsx
+++ b/Database.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Charlie\Non Puriel\Adress-Shack\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6E61C24-B86A-4C35-883D-A7845DEEA5F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15272C64-04BF-4BA4-AD37-742F6F3B7A4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Address Book" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191028"/>

--- a/Database.xlsx
+++ b/Database.xlsx
@@ -8,13 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Charlie\Non Puriel\Adress-Shack\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15272C64-04BF-4BA4-AD37-742F6F3B7A4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9B28A53-4F44-465A-AB18-05B757F89A70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Address Book" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="SampleData" sheetId="2" r:id="rId1"/>
+    <sheet name="Address Book" sheetId="1" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -670,6 +670,442 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F28EEB29-88E9-4F91-A919-2DF8C70E2648}">
+  <dimension ref="A1:G20"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="2" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="255.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="3.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E1" t="b">
+        <v>1</v>
+      </c>
+      <c r="F1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2" t="b">
+        <v>0</v>
+      </c>
+      <c r="F2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3">
+        <v>2</v>
+      </c>
+      <c r="D3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E3" t="b">
+        <v>1</v>
+      </c>
+      <c r="F3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>55</v>
+      </c>
+      <c r="B4" t="s">
+        <v>53</v>
+      </c>
+      <c r="D4">
+        <v>11</v>
+      </c>
+      <c r="E4" t="b">
+        <v>1</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="G4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>56</v>
+      </c>
+      <c r="B5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" t="s">
+        <v>57</v>
+      </c>
+      <c r="D5" t="s">
+        <v>22</v>
+      </c>
+      <c r="E5" t="b">
+        <v>0</v>
+      </c>
+      <c r="F5" t="s">
+        <v>58</v>
+      </c>
+      <c r="G5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>59</v>
+      </c>
+      <c r="B6" t="s">
+        <v>60</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6" t="s">
+        <v>61</v>
+      </c>
+      <c r="E6" t="b">
+        <v>0</v>
+      </c>
+      <c r="F6" t="s">
+        <v>55</v>
+      </c>
+      <c r="G6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>62</v>
+      </c>
+      <c r="B7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" t="s">
+        <v>22</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
+      </c>
+      <c r="E7" t="b">
+        <v>0</v>
+      </c>
+      <c r="F7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G7">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>55</v>
+      </c>
+      <c r="B8" t="s">
+        <v>63</v>
+      </c>
+      <c r="C8" t="s">
+        <v>22</v>
+      </c>
+      <c r="D8">
+        <v>1</v>
+      </c>
+      <c r="E8" t="b">
+        <v>1</v>
+      </c>
+      <c r="F8" t="s">
+        <v>22</v>
+      </c>
+      <c r="G8">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>64</v>
+      </c>
+      <c r="B9" t="s">
+        <v>63</v>
+      </c>
+      <c r="C9">
+        <v>1</v>
+      </c>
+      <c r="D9">
+        <v>11</v>
+      </c>
+      <c r="E9" t="b">
+        <v>1</v>
+      </c>
+      <c r="F9" t="s">
+        <v>22</v>
+      </c>
+      <c r="G9">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>1</v>
+      </c>
+      <c r="B10">
+        <v>2</v>
+      </c>
+      <c r="C10">
+        <v>4</v>
+      </c>
+      <c r="D10">
+        <v>3</v>
+      </c>
+      <c r="E10" t="b">
+        <v>0</v>
+      </c>
+      <c r="F10">
+        <v>5</v>
+      </c>
+      <c r="G10">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>59</v>
+      </c>
+      <c r="B11" t="s">
+        <v>60</v>
+      </c>
+      <c r="C11">
+        <v>1</v>
+      </c>
+      <c r="D11">
+        <v>1</v>
+      </c>
+      <c r="E11" t="b">
+        <v>0</v>
+      </c>
+      <c r="F11" t="s">
+        <v>55</v>
+      </c>
+      <c r="G11">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>65</v>
+      </c>
+      <c r="B12" t="s">
+        <v>66</v>
+      </c>
+      <c r="C12">
+        <v>1234567891</v>
+      </c>
+      <c r="D12" t="s">
+        <v>22</v>
+      </c>
+      <c r="E12" t="b">
+        <v>1</v>
+      </c>
+      <c r="F12" t="s">
+        <v>67</v>
+      </c>
+      <c r="G12">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>22</v>
+      </c>
+      <c r="B13" t="s">
+        <v>22</v>
+      </c>
+      <c r="C13">
+        <v>12</v>
+      </c>
+      <c r="D13" t="s">
+        <v>68</v>
+      </c>
+      <c r="E13" t="b">
+        <v>1</v>
+      </c>
+      <c r="F13" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>22</v>
+      </c>
+      <c r="B14" t="s">
+        <v>54</v>
+      </c>
+      <c r="C14">
+        <v>1</v>
+      </c>
+      <c r="D14" t="s">
+        <v>70</v>
+      </c>
+      <c r="E14" t="b">
+        <v>1</v>
+      </c>
+      <c r="F14" t="s">
+        <v>59</v>
+      </c>
+      <c r="G14">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>71</v>
+      </c>
+      <c r="E15" t="b">
+        <v>0</v>
+      </c>
+      <c r="G15">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>59</v>
+      </c>
+      <c r="E16" t="b">
+        <v>0</v>
+      </c>
+      <c r="G16">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>59</v>
+      </c>
+      <c r="E17" t="b">
+        <v>0</v>
+      </c>
+      <c r="G17">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>22</v>
+      </c>
+      <c r="B18" t="s">
+        <v>22</v>
+      </c>
+      <c r="C18">
+        <v>12</v>
+      </c>
+      <c r="D18" t="s">
+        <v>68</v>
+      </c>
+      <c r="E18" t="b">
+        <v>1</v>
+      </c>
+      <c r="F18" t="s">
+        <v>72</v>
+      </c>
+      <c r="G18">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>1</v>
+      </c>
+      <c r="B19">
+        <v>1</v>
+      </c>
+      <c r="C19">
+        <v>1234567890</v>
+      </c>
+      <c r="D19">
+        <v>1</v>
+      </c>
+      <c r="E19" t="b">
+        <v>0</v>
+      </c>
+      <c r="F19" t="s">
+        <v>73</v>
+      </c>
+      <c r="G19">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>22</v>
+      </c>
+      <c r="B20" t="s">
+        <v>22</v>
+      </c>
+      <c r="C20">
+        <v>1</v>
+      </c>
+      <c r="D20" t="s">
+        <v>54</v>
+      </c>
+      <c r="E20" t="b">
+        <v>1</v>
+      </c>
+      <c r="F20" t="s">
+        <v>22</v>
+      </c>
+      <c r="G20">
+        <v>20</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AC24"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1119,440 +1555,4 @@
     <tablePart r:id="rId11"/>
   </tableParts>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F28EEB29-88E9-4F91-A919-2DF8C70E2648}">
-  <dimension ref="A1:G20"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="2" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="5.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="255.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="3.28515625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C1">
-        <v>1</v>
-      </c>
-      <c r="D1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E1" t="b">
-        <v>1</v>
-      </c>
-      <c r="F1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B2" t="s">
-        <v>54</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E2" t="b">
-        <v>0</v>
-      </c>
-      <c r="F2" t="s">
-        <v>22</v>
-      </c>
-      <c r="G2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C3">
-        <v>2</v>
-      </c>
-      <c r="D3" t="s">
-        <v>22</v>
-      </c>
-      <c r="E3" t="b">
-        <v>1</v>
-      </c>
-      <c r="F3" t="s">
-        <v>22</v>
-      </c>
-      <c r="G3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>55</v>
-      </c>
-      <c r="B4" t="s">
-        <v>53</v>
-      </c>
-      <c r="D4">
-        <v>11</v>
-      </c>
-      <c r="E4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F4">
-        <v>1</v>
-      </c>
-      <c r="G4">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>56</v>
-      </c>
-      <c r="B5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C5" t="s">
-        <v>57</v>
-      </c>
-      <c r="D5" t="s">
-        <v>22</v>
-      </c>
-      <c r="E5" t="b">
-        <v>0</v>
-      </c>
-      <c r="F5" t="s">
-        <v>58</v>
-      </c>
-      <c r="G5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>59</v>
-      </c>
-      <c r="B6" t="s">
-        <v>60</v>
-      </c>
-      <c r="C6">
-        <v>1</v>
-      </c>
-      <c r="D6" t="s">
-        <v>61</v>
-      </c>
-      <c r="E6" t="b">
-        <v>0</v>
-      </c>
-      <c r="F6" t="s">
-        <v>55</v>
-      </c>
-      <c r="G6">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>62</v>
-      </c>
-      <c r="B7" t="s">
-        <v>22</v>
-      </c>
-      <c r="C7" t="s">
-        <v>22</v>
-      </c>
-      <c r="D7">
-        <v>1</v>
-      </c>
-      <c r="E7" t="b">
-        <v>0</v>
-      </c>
-      <c r="F7" t="s">
-        <v>22</v>
-      </c>
-      <c r="G7">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>55</v>
-      </c>
-      <c r="B8" t="s">
-        <v>63</v>
-      </c>
-      <c r="C8" t="s">
-        <v>22</v>
-      </c>
-      <c r="D8">
-        <v>1</v>
-      </c>
-      <c r="E8" t="b">
-        <v>1</v>
-      </c>
-      <c r="F8" t="s">
-        <v>22</v>
-      </c>
-      <c r="G8">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>64</v>
-      </c>
-      <c r="B9" t="s">
-        <v>63</v>
-      </c>
-      <c r="C9">
-        <v>1</v>
-      </c>
-      <c r="D9">
-        <v>11</v>
-      </c>
-      <c r="E9" t="b">
-        <v>1</v>
-      </c>
-      <c r="F9" t="s">
-        <v>22</v>
-      </c>
-      <c r="G9">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10">
-        <v>1</v>
-      </c>
-      <c r="B10">
-        <v>2</v>
-      </c>
-      <c r="C10">
-        <v>4</v>
-      </c>
-      <c r="D10">
-        <v>3</v>
-      </c>
-      <c r="E10" t="b">
-        <v>0</v>
-      </c>
-      <c r="F10">
-        <v>5</v>
-      </c>
-      <c r="G10">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>59</v>
-      </c>
-      <c r="B11" t="s">
-        <v>60</v>
-      </c>
-      <c r="C11">
-        <v>1</v>
-      </c>
-      <c r="D11">
-        <v>1</v>
-      </c>
-      <c r="E11" t="b">
-        <v>0</v>
-      </c>
-      <c r="F11" t="s">
-        <v>55</v>
-      </c>
-      <c r="G11">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>65</v>
-      </c>
-      <c r="B12" t="s">
-        <v>66</v>
-      </c>
-      <c r="C12">
-        <v>1234567891</v>
-      </c>
-      <c r="D12" t="s">
-        <v>22</v>
-      </c>
-      <c r="E12" t="b">
-        <v>1</v>
-      </c>
-      <c r="F12" t="s">
-        <v>67</v>
-      </c>
-      <c r="G12">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>22</v>
-      </c>
-      <c r="B13" t="s">
-        <v>22</v>
-      </c>
-      <c r="C13">
-        <v>12</v>
-      </c>
-      <c r="D13" t="s">
-        <v>68</v>
-      </c>
-      <c r="E13" t="b">
-        <v>1</v>
-      </c>
-      <c r="F13" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>22</v>
-      </c>
-      <c r="B14" t="s">
-        <v>54</v>
-      </c>
-      <c r="C14">
-        <v>1</v>
-      </c>
-      <c r="D14" t="s">
-        <v>70</v>
-      </c>
-      <c r="E14" t="b">
-        <v>1</v>
-      </c>
-      <c r="F14" t="s">
-        <v>59</v>
-      </c>
-      <c r="G14">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>71</v>
-      </c>
-      <c r="E15" t="b">
-        <v>0</v>
-      </c>
-      <c r="G15">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>59</v>
-      </c>
-      <c r="E16" t="b">
-        <v>0</v>
-      </c>
-      <c r="G16">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>59</v>
-      </c>
-      <c r="E17" t="b">
-        <v>0</v>
-      </c>
-      <c r="G17">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>22</v>
-      </c>
-      <c r="B18" t="s">
-        <v>22</v>
-      </c>
-      <c r="C18">
-        <v>12</v>
-      </c>
-      <c r="D18" t="s">
-        <v>68</v>
-      </c>
-      <c r="E18" t="b">
-        <v>1</v>
-      </c>
-      <c r="F18" t="s">
-        <v>72</v>
-      </c>
-      <c r="G18">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19">
-        <v>1</v>
-      </c>
-      <c r="B19">
-        <v>1</v>
-      </c>
-      <c r="C19">
-        <v>1234567890</v>
-      </c>
-      <c r="D19">
-        <v>1</v>
-      </c>
-      <c r="E19" t="b">
-        <v>0</v>
-      </c>
-      <c r="F19" t="s">
-        <v>73</v>
-      </c>
-      <c r="G19">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>22</v>
-      </c>
-      <c r="B20" t="s">
-        <v>22</v>
-      </c>
-      <c r="C20">
-        <v>1</v>
-      </c>
-      <c r="D20" t="s">
-        <v>54</v>
-      </c>
-      <c r="E20" t="b">
-        <v>1</v>
-      </c>
-      <c r="F20" t="s">
-        <v>22</v>
-      </c>
-      <c r="G20">
-        <v>20</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/Database.xlsx
+++ b/Database.xlsx
@@ -8,13 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Charlie\Non Puriel\Adress-Shack\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9B28A53-4F44-465A-AB18-05B757F89A70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7A32B10-FA57-4508-AE1B-4A72A7196261}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SampleData" sheetId="2" r:id="rId1"/>
     <sheet name="Address Book" sheetId="1" r:id="rId2"/>
+    <sheet name="Inventory" sheetId="4" r:id="rId3"/>
+    <sheet name="Vending" sheetId="5" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -1555,4 +1557,22 @@
     <tablePart r:id="rId11"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C7BC218-E894-43DE-BEC3-7A8A07868B41}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E27DB38-9B86-476F-ADB3-257C50139E20}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Database.xlsx
+++ b/Database.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Charlie\Non Puriel\Adress-Shack\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7A32B10-FA57-4508-AE1B-4A72A7196261}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1438BD5-B60E-4EA7-A790-398B235C4544}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SampleData" sheetId="2" r:id="rId1"/>
     <sheet name="Address Book" sheetId="1" r:id="rId2"/>
-    <sheet name="Inventory" sheetId="4" r:id="rId3"/>
+    <sheet name="Snacks" sheetId="4" r:id="rId3"/>
     <sheet name="Vending" sheetId="5" r:id="rId4"/>
+    <sheet name="Sales" sheetId="6" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -1575,4 +1576,13 @@
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1932462C-482C-40F7-8C16-E10683B0C6A3}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Database.xlsx
+++ b/Database.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Charlie\Non Puriel\Adress-Shack\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1438BD5-B60E-4EA7-A790-398B235C4544}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F088E41-FB1B-4E9E-A3DC-03DB4FC77C33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="88">
   <si>
     <t>Index</t>
   </si>
@@ -284,6 +284,30 @@
   </si>
   <si>
     <t>?</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Price</t>
+  </si>
+  <si>
+    <t>Quantity On Hand</t>
+  </si>
+  <si>
+    <t>Image Path</t>
+  </si>
+  <si>
+    <t>Field</t>
+  </si>
+  <si>
+    <t>C# Data Type</t>
+  </si>
+  <si>
+    <t>SQL Datatype</t>
+  </si>
+  <si>
+    <t>description</t>
   </si>
 </sst>
 </file>
@@ -372,6 +396,19 @@
     <tableColumn id="5" xr3:uid="{E2103641-138F-4A73-BF67-1811A710432C}" name="Email"/>
     <tableColumn id="6" xr3:uid="{8F980FE7-396A-4C67-ACCF-1467F50B1A65}" name="Type"/>
     <tableColumn id="7" xr3:uid="{39796BF6-4406-43D7-92DC-E7AF93650D3F}" name="Notes"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{A47B01E8-8101-4DDF-8AB7-5C5FCA655866}" name="Table2" displayName="Table2" ref="A1:D5" totalsRowShown="0">
+  <autoFilter ref="A1:D5" xr:uid="{A47B01E8-8101-4DDF-8AB7-5C5FCA655866}"/>
+  <tableColumns count="4">
+    <tableColumn id="1" xr3:uid="{E195EB5F-6D4B-42C3-8801-919637F30006}" name="Name"/>
+    <tableColumn id="2" xr3:uid="{4B91A874-5D42-4D28-8019-43E3F99D2B4B}" name="Price"/>
+    <tableColumn id="3" xr3:uid="{191A4393-993C-4AB5-9310-5337B03C07D3}" name="Quantity On Hand"/>
+    <tableColumn id="4" xr3:uid="{01AF8722-0E57-4D45-8F72-AD068B958406}" name="Image Path"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1562,10 +1599,47 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C7BC218-E894-43DE-BEC3-7A8A07868B41}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:J1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <cols>
+    <col min="3" max="3" width="18.85546875" customWidth="1"/>
+    <col min="4" max="4" width="13" customWidth="1"/>
+    <col min="8" max="8" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C1" t="s">
+        <v>82</v>
+      </c>
+      <c r="D1" t="s">
+        <v>83</v>
+      </c>
+      <c r="G1" t="s">
+        <v>84</v>
+      </c>
+      <c r="H1" t="s">
+        <v>85</v>
+      </c>
+      <c r="I1" t="s">
+        <v>86</v>
+      </c>
+      <c r="J1" t="s">
+        <v>87</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
 

--- a/Database.xlsx
+++ b/Database.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Charlie\Non Puriel\Adress-Shack\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F088E41-FB1B-4E9E-A3DC-03DB4FC77C33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9EAF495-0CCA-4E3B-AFE8-CC28CA58D7A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="89">
   <si>
     <t>Index</t>
   </si>
@@ -308,6 +308,9 @@
   </si>
   <si>
     <t>description</t>
+  </si>
+  <si>
+    <t>Quantity</t>
   </si>
 </sst>
 </file>
@@ -1599,11 +1602,12 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C7BC218-E894-43DE-BEC3-7A8A07868B41}">
-  <dimension ref="A1:J1"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="18.85546875" customWidth="1"/>
     <col min="4" max="4" width="13" customWidth="1"/>
+    <col min="7" max="7" width="10.85546875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12.28515625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="12.7109375" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="11" bestFit="1" customWidth="1"/>
@@ -1633,6 +1637,26 @@
       </c>
       <c r="J1" t="s">
         <v>87</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="G2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="G3" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="G4" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="G5" t="s">
+        <v>83</v>
       </c>
     </row>
   </sheetData>

--- a/Database.xlsx
+++ b/Database.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Charlie\Non Puriel\Adress-Shack\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9EAF495-0CCA-4E3B-AFE8-CC28CA58D7A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABB39572-74E8-4408-BC41-92ADF6142599}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="91">
   <si>
     <t>Index</t>
   </si>
@@ -311,6 +311,12 @@
   </si>
   <si>
     <t>Quantity</t>
+  </si>
+  <si>
+    <t>char(15)</t>
+  </si>
+  <si>
+    <t>name of the snack</t>
   </si>
 </sst>
 </file>
@@ -1643,6 +1649,15 @@
       <c r="G2" t="s">
         <v>80</v>
       </c>
+      <c r="H2" t="s">
+        <v>35</v>
+      </c>
+      <c r="I2" t="s">
+        <v>89</v>
+      </c>
+      <c r="J2" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="G3" t="s">

--- a/Database.xlsx
+++ b/Database.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Charlie\Non Puriel\Adress-Shack\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABB39572-74E8-4408-BC41-92ADF6142599}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CC3192C-50E7-441D-9BA7-A0777BAC31F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="97">
   <si>
     <t>Index</t>
   </si>
@@ -317,6 +317,24 @@
   </si>
   <si>
     <t>name of the snack</t>
+  </si>
+  <si>
+    <t>decimal</t>
+  </si>
+  <si>
+    <t>decimal(10)</t>
+  </si>
+  <si>
+    <t>price of snack</t>
+  </si>
+  <si>
+    <t>int</t>
+  </si>
+  <si>
+    <t>smallint(5)</t>
+  </si>
+  <si>
+    <t>quantity of snack</t>
   </si>
 </sst>
 </file>
@@ -1663,10 +1681,28 @@
       <c r="G3" t="s">
         <v>81</v>
       </c>
+      <c r="H3" t="s">
+        <v>91</v>
+      </c>
+      <c r="I3" t="s">
+        <v>92</v>
+      </c>
+      <c r="J3" t="s">
+        <v>93</v>
+      </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="G4" t="s">
         <v>88</v>
+      </c>
+      <c r="H4" t="s">
+        <v>94</v>
+      </c>
+      <c r="I4" t="s">
+        <v>95</v>
+      </c>
+      <c r="J4" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">

--- a/Database.xlsx
+++ b/Database.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Charlie\Non Puriel\Adress-Shack\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CC3192C-50E7-441D-9BA7-A0777BAC31F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F1596D0-5FD3-4570-BF49-D03C42A3DE84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="98">
   <si>
     <t>Index</t>
   </si>
@@ -335,6 +335,9 @@
   </si>
   <si>
     <t>quantity of snack</t>
+  </si>
+  <si>
+    <t>path of image</t>
   </si>
 </sst>
 </file>
@@ -1709,6 +1712,15 @@
       <c r="G5" t="s">
         <v>83</v>
       </c>
+      <c r="H5" t="s">
+        <v>35</v>
+      </c>
+      <c r="I5" t="s">
+        <v>76</v>
+      </c>
+      <c r="J5" t="s">
+        <v>97</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Database.xlsx
+++ b/Database.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Charlie\Non Puriel\Adress-Shack\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F1596D0-5FD3-4570-BF49-D03C42A3DE84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A06C6D02-D906-412B-8942-AB16C987B31B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -319,9 +319,6 @@
     <t>name of the snack</t>
   </si>
   <si>
-    <t>decimal</t>
-  </si>
-  <si>
     <t>decimal(10)</t>
   </si>
   <si>
@@ -338,6 +335,9 @@
   </si>
   <si>
     <t>path of image</t>
+  </si>
+  <si>
+    <t>float</t>
   </si>
 </sst>
 </file>
@@ -1685,13 +1685,13 @@
         <v>81</v>
       </c>
       <c r="H3" t="s">
+        <v>97</v>
+      </c>
+      <c r="I3" t="s">
         <v>91</v>
       </c>
-      <c r="I3" t="s">
+      <c r="J3" t="s">
         <v>92</v>
-      </c>
-      <c r="J3" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
@@ -1699,13 +1699,13 @@
         <v>88</v>
       </c>
       <c r="H4" t="s">
+        <v>93</v>
+      </c>
+      <c r="I4" t="s">
         <v>94</v>
       </c>
-      <c r="I4" t="s">
+      <c r="J4" t="s">
         <v>95</v>
-      </c>
-      <c r="J4" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -1719,7 +1719,7 @@
         <v>76</v>
       </c>
       <c r="J5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
   </sheetData>

--- a/Database.xlsx
+++ b/Database.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Charlie\Non Puriel\Adress-Shack\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A06C6D02-D906-412B-8942-AB16C987B31B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC0197D7-00EA-4E74-BF0A-9A2FB0A54725}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -313,15 +313,9 @@
     <t>Quantity</t>
   </si>
   <si>
-    <t>char(15)</t>
-  </si>
-  <si>
     <t>name of the snack</t>
   </si>
   <si>
-    <t>decimal(10)</t>
-  </si>
-  <si>
     <t>price of snack</t>
   </si>
   <si>
@@ -338,6 +332,12 @@
   </si>
   <si>
     <t>float</t>
+  </si>
+  <si>
+    <t>char(30)</t>
+  </si>
+  <si>
+    <t>smallmoney</t>
   </si>
 </sst>
 </file>
@@ -1674,10 +1674,10 @@
         <v>35</v>
       </c>
       <c r="I2" t="s">
+        <v>96</v>
+      </c>
+      <c r="J2" t="s">
         <v>89</v>
-      </c>
-      <c r="J2" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
@@ -1685,13 +1685,13 @@
         <v>81</v>
       </c>
       <c r="H3" t="s">
+        <v>95</v>
+      </c>
+      <c r="I3" t="s">
         <v>97</v>
       </c>
-      <c r="I3" t="s">
-        <v>91</v>
-      </c>
       <c r="J3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
@@ -1699,13 +1699,13 @@
         <v>88</v>
       </c>
       <c r="H4" t="s">
+        <v>91</v>
+      </c>
+      <c r="I4" t="s">
+        <v>92</v>
+      </c>
+      <c r="J4" t="s">
         <v>93</v>
-      </c>
-      <c r="I4" t="s">
-        <v>94</v>
-      </c>
-      <c r="J4" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -1719,7 +1719,7 @@
         <v>76</v>
       </c>
       <c r="J5" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
   </sheetData>

--- a/Database.xlsx
+++ b/Database.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Charlie\Non Puriel\Adress-Shack\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC0197D7-00EA-4E74-BF0A-9A2FB0A54725}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3D8EB3A-5391-4E71-9E8C-3ACFDD5EE9F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -322,9 +322,6 @@
     <t>int</t>
   </si>
   <si>
-    <t>smallint(5)</t>
-  </si>
-  <si>
     <t>quantity of snack</t>
   </si>
   <si>
@@ -338,6 +335,9 @@
   </si>
   <si>
     <t>smallmoney</t>
+  </si>
+  <si>
+    <t>tinyint</t>
   </si>
 </sst>
 </file>
@@ -1674,7 +1674,7 @@
         <v>35</v>
       </c>
       <c r="I2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="J2" t="s">
         <v>89</v>
@@ -1685,10 +1685,10 @@
         <v>81</v>
       </c>
       <c r="H3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="J3" t="s">
         <v>90</v>
@@ -1702,10 +1702,10 @@
         <v>91</v>
       </c>
       <c r="I4" t="s">
+        <v>97</v>
+      </c>
+      <c r="J4" t="s">
         <v>92</v>
-      </c>
-      <c r="J4" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -1719,7 +1719,7 @@
         <v>76</v>
       </c>
       <c r="J5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
   </sheetData>

--- a/Database.xlsx
+++ b/Database.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Charlie\Non Puriel\Adress-Shack\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3D8EB3A-5391-4E71-9E8C-3ACFDD5EE9F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{887FAF4C-3ED9-4395-A187-B70C8C0AC3BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="100">
   <si>
     <t>Index</t>
   </si>
@@ -338,6 +338,12 @@
   </si>
   <si>
     <t>tinyint</t>
+  </si>
+  <si>
+    <t>identifier</t>
+  </si>
+  <si>
+    <t>SnackID</t>
   </si>
 </sst>
 </file>
@@ -432,9 +438,10 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{A47B01E8-8101-4DDF-8AB7-5C5FCA655866}" name="Table2" displayName="Table2" ref="A1:D5" totalsRowShown="0">
-  <autoFilter ref="A1:D5" xr:uid="{A47B01E8-8101-4DDF-8AB7-5C5FCA655866}"/>
-  <tableColumns count="4">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{A47B01E8-8101-4DDF-8AB7-5C5FCA655866}" name="Table2" displayName="Table2" ref="A1:E5" totalsRowShown="0">
+  <autoFilter ref="A1:E5" xr:uid="{A47B01E8-8101-4DDF-8AB7-5C5FCA655866}"/>
+  <tableColumns count="5">
+    <tableColumn id="5" xr3:uid="{16675459-3146-4AB1-AF33-2448F18FFD91}" name="SnackID"/>
     <tableColumn id="1" xr3:uid="{E195EB5F-6D4B-42C3-8801-919637F30006}" name="Name"/>
     <tableColumn id="2" xr3:uid="{4B91A874-5D42-4D28-8019-43E3F99D2B4B}" name="Price"/>
     <tableColumn id="3" xr3:uid="{191A4393-993C-4AB5-9310-5337B03C07D3}" name="Quantity On Hand"/>
@@ -1629,9 +1636,10 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C7BC218-E894-43DE-BEC3-7A8A07868B41}">
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:K7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="1" max="1" width="10.140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="18.85546875" customWidth="1"/>
     <col min="4" max="4" width="13" customWidth="1"/>
     <col min="7" max="7" width="10.85546875" bestFit="1" customWidth="1"/>
@@ -1640,86 +1648,94 @@
     <col min="10" max="10" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>99</v>
+      </c>
+      <c r="B1" t="s">
         <v>80</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>81</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>82</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>83</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>84</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>85</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>86</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="G2" t="s">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="H2" t="s">
         <v>80</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>35</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>95</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="G3" t="s">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="H3" t="s">
         <v>81</v>
       </c>
-      <c r="H3" t="s">
+      <c r="I3" t="s">
         <v>94</v>
       </c>
-      <c r="I3" t="s">
+      <c r="J3" t="s">
         <v>96</v>
       </c>
-      <c r="J3" t="s">
+      <c r="K3" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="G4" t="s">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="H4" t="s">
         <v>88</v>
       </c>
-      <c r="H4" t="s">
+      <c r="I4" t="s">
         <v>91</v>
       </c>
-      <c r="I4" t="s">
+      <c r="J4" t="s">
         <v>97</v>
       </c>
-      <c r="J4" t="s">
+      <c r="K4" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="G5" t="s">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="H5" t="s">
         <v>83</v>
       </c>
-      <c r="H5" t="s">
+      <c r="I5" t="s">
         <v>35</v>
       </c>
-      <c r="I5" t="s">
+      <c r="J5" t="s">
         <v>76</v>
       </c>
-      <c r="J5" t="s">
+      <c r="K5" t="s">
         <v>93</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="G7" t="s">
+        <v>98</v>
       </c>
     </row>
   </sheetData>

--- a/Database.xlsx
+++ b/Database.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Charlie\Non Puriel\Adress-Shack\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{887FAF4C-3ED9-4395-A187-B70C8C0AC3BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4733EC11-5F02-409D-92BF-4625A861D9C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="100">
   <si>
     <t>Index</t>
   </si>
@@ -340,10 +340,10 @@
     <t>tinyint</t>
   </si>
   <si>
-    <t>identifier</t>
-  </si>
-  <si>
     <t>SnackID</t>
+  </si>
+  <si>
+    <t>uuid for said entry</t>
   </si>
 </sst>
 </file>
@@ -1636,7 +1636,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C7BC218-E894-43DE-BEC3-7A8A07868B41}">
-  <dimension ref="A1:K7"/>
+  <dimension ref="A1:K6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.140625" bestFit="1" customWidth="1"/>
@@ -1650,7 +1650,7 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B1" t="s">
         <v>80</v>
@@ -1679,63 +1679,72 @@
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="H2" t="s">
-        <v>80</v>
+        <v>98</v>
       </c>
       <c r="I2" t="s">
-        <v>35</v>
+        <v>91</v>
       </c>
       <c r="J2" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="K2" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="H3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="I3" t="s">
-        <v>94</v>
+        <v>35</v>
       </c>
       <c r="J3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="K3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="H4" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="I4" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="J4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="K4" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="H5" t="s">
+        <v>88</v>
+      </c>
+      <c r="I5" t="s">
+        <v>91</v>
+      </c>
+      <c r="J5" t="s">
+        <v>97</v>
+      </c>
+      <c r="K5" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="H6" t="s">
         <v>83</v>
       </c>
-      <c r="I5" t="s">
+      <c r="I6" t="s">
         <v>35</v>
       </c>
-      <c r="J5" t="s">
+      <c r="J6" t="s">
         <v>76</v>
       </c>
-      <c r="K5" t="s">
+      <c r="K6" t="s">
         <v>93</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="G7" t="s">
-        <v>98</v>
       </c>
     </row>
   </sheetData>
